--- a/questionnaire_templates/006_early_childhood_math_skills_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/006_early_childhood_math_skills_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>basic_numbers</t>
+          <t>basic numbers</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>place_value</t>
+          <t>place value</t>
         </is>
       </c>
     </row>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ten_thousands</t>
+          <t>ten thousands</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>counting_money</t>
+          <t>counting money</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>comparing_money</t>
+          <t>comparing money</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>making_change</t>
+          <t>making change</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>counting_time</t>
+          <t>counting time</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>telling_time</t>
+          <t>telling time</t>
         </is>
       </c>
     </row>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>understanding_time</t>
+          <t>understanding time</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>math_in_words</t>
+          <t>math in words</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>math_with_numbers</t>
+          <t>math with numbers</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>math_with</t>
+          <t>math with</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>basic_problem_solving</t>
+          <t>basic problem solving</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>complex_problem_solving</t>
+          <t>complex problem solving</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>making_connections</t>
+          <t>making connections</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>math_emotional_intelligence</t>
+          <t>math emotional intelligence</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>math_anxiety</t>
+          <t>math anxiety</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>math_confidence</t>
+          <t>math confidence</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>math_attention_span</t>
+          <t>math attention span</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>math_focus</t>
+          <t>math focus</t>
         </is>
       </c>
     </row>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>math_sustained_effort</t>
+          <t>math sustained effort</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>counting_conceptualization</t>
+          <t>counting conceptualization</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>place_value_conceptualization</t>
+          <t>place value conceptualization</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>money_conceptualization</t>
+          <t>money conceptualization</t>
         </is>
       </c>
     </row>
